--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Etapas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Itens" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cotações" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fornecedores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Etapas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Itens" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cotações" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Comparativo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Revisões" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Fornecedores" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Etapas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Itens" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cotações" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Comparativo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Revisões" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Fornecedores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Etapas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Itens" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cotações" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fornecedores" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 02:02 (BRT)</t>
+          <t>Gerada em 16/07/2026 13:49 (BRT)</t>
         </is>
       </c>
     </row>
@@ -927,6 +927,18 @@
       <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Radier ~103 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Térreo — faixa SO</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Despensa + banheiro completo (1,50 × 2,20) + lavabo (1,50 × 1,50) no fundo da cozinha · janelas p/ o acesso lateral · porta do lavabo direto p/ a varanda gourmet</t>
         </is>
       </c>
     </row>
@@ -947,11 +959,12 @@
     <row r="31"/>
     <row r="32"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A30:D32"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B24:D24"/>
@@ -1844,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4230,7 +4243,7 @@
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
-          <t>suíte, banheiro do quarto e banheiro térreo · caimento 2% na impermeabilização</t>
+          <t>suíte, banheiro do quarto e banheiro do térreo (agora no fundo da cozinha, faixa SO)</t>
         </is>
       </c>
     </row>
@@ -10037,6 +10050,179 @@
       <c r="M146" s="21" t="inlineStr">
         <is>
           <t>cotar empreiteiro/equipe separadamente do material · preencher o Fornecedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>IT144</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>Lavabo do térreo — vaso + cuba + torneira + sifão</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr">
+        <is>
+          <t>lavabo 1,50 × 1,50 no canto SO/SE, porta p/ a varanda</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>cj</t>
+        </is>
+      </c>
+      <c r="H147" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A147)</f>
+        <v/>
+      </c>
+      <c r="J147" s="32">
+        <f>IF(I147=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A147))</f>
+        <v/>
+      </c>
+      <c r="K147" s="17">
+        <f>IF(I147=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A147)*(Cotações!$J$2:$J$2=J147),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L147" s="18">
+        <f>IF(I147=0,"—",IFERROR(J147*H147,""))</f>
+        <v/>
+      </c>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>ponto novo: ramal de esgoto e água aproveita a prumada do banheiro vizinho (paredes coladas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="21" t="inlineStr">
+        <is>
+          <t>IT145</t>
+        </is>
+      </c>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C148" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" s="21" t="inlineStr">
+        <is>
+          <t>Ramal hidráulico do lavabo (água fria + esgoto + ventilação)</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="inlineStr"/>
+      <c r="G148" s="21" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H148" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A148)</f>
+        <v/>
+      </c>
+      <c r="J148" s="30">
+        <f>IF(I148=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A148))</f>
+        <v/>
+      </c>
+      <c r="K148" s="22">
+        <f>IF(I148=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A148)*(Cotações!$J$2:$J$2=J148),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L148" s="23">
+        <f>IF(I148=0,"—",IFERROR(J148*H148,""))</f>
+        <v/>
+      </c>
+      <c r="M148" s="21" t="inlineStr">
+        <is>
+          <t>economia: banheiro e lavabo compartilham a mesma parede hidráulica</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>IT146</t>
+        </is>
+      </c>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>Acabamento do lavabo do térreo — microcimento + piso resinado</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr">
+        <is>
+          <t>paredes + piso · sem carpete de pedra (lavabo seco)</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H149" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="I149" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A149)</f>
+        <v/>
+      </c>
+      <c r="J149" s="32">
+        <f>IF(I149=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A149))</f>
+        <v/>
+      </c>
+      <c r="K149" s="17">
+        <f>IF(I149=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A149)*(Cotações!$J$2:$J$2=J149),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L149" s="18">
+        <f>IF(I149=0,"—",IFERROR(J149*H149,""))</f>
+        <v/>
+      </c>
+      <c r="M149" s="16" t="inlineStr">
+        <is>
+          <t>DIY viável — ambiente pequeno e sem área molhada</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10865,6 +11051,23 @@
       <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Material e mão de obra separados por etapa e por fornecedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Térreo: banheiro sai da parede da garagem → banheiro + lavabo no fundo da cozinha (faixa SO)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Cozinha 36 → 29 m² · +1 lavabo · janelas p/ o acesso lateral · porta do lavabo p/ a varanda</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Etapas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Itens" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cotações" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisões" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fornecedores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Etapas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Itens" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cotações" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Comparativo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Revisões" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Fornecedores" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 13:49 (BRT)</t>
+          <t>Gerada em 16/07/2026 13:51 (BRT)</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 13:51 (BRT)</t>
+          <t>Gerada em 16/07/2026 15:33 (BRT)</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Faixa NE</t>
+          <t>Faixa NE (1,20)</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Área de luz descoberta até a fachada, dividida em 2 por parede cega: Luz 1 = jardim de inverno c/ parede verde e janelão 3,50; Luz 2 = varal/serve a lavanderia</t>
+          <t>Da fachada ao fundo: portinha (0,80) · Luz 1 = jardim de inverno c/ parede verde e janelão 3,50 (4,10) · PAREDE CEGA · Luz 2 = varal (4,10) · lavanderia + área técnica acima (4,00, único trecho coberto até a divisa)</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="H7" s="31" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="16">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A7)</f>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="H11" s="31" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I11" s="16">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A11)</f>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>não cobre a faixa de luz (9,70 × 1,20 descoberta)</t>
+          <t>não cobre a faixa de luz (8,20 × 1,20 descoberta) · cobre serviço/técnica (4,00 × 1,20)</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F125" s="16" t="inlineStr">
         <is>
-          <t>~1,20 × 4,85 × h ~3 m ≈ 14 m² · painéis modulares ou treliça c/ trepadeiras</t>
+          <t>~1,20 × 4,10 × h ~3 m ≈ 12 m² · painéis modulares ou treliça c/ trepadeiras</t>
         </is>
       </c>
       <c r="G125" s="16" t="inlineStr">
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="H125" s="31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I125" s="16">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A125)</f>
@@ -10801,7 +10801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11068,6 +11068,40 @@
       <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Cozinha 36 → 29 m² · +1 lavabo · janelas p/ o acesso lateral · porta do lavabo p/ a varanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Porta da lavanderia a 0,90 da parede do fundo</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Máquina sob a janela do fundo + nicho de geladeira no canto da cozinha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Lavanderia/técnica 2,50 → 4,00 m; Luz 1 e Luz 2 4,85 → 4,10 m cada</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Faixa de luz 9,70 → 8,20 m · laje 68 → 70 m² · telha 98 → 100 m² · parede verde 14 → 12 m²</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 15:33 (BRT)</t>
+          <t>Gerada em 16/07/2026 15:45 (BRT)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Despensa + banheiro completo (1,50 × 2,20) + lavabo (1,50 × 1,50) no fundo da cozinha · janelas p/ o acesso lateral · porta do lavabo direto p/ a varanda gourmet</t>
+          <t>Despensa (1,50 × 1,10) + bancada + banheiro completo único (1,50 × 2,50, sem box) no canto do fundo · janela p/ o acesso lateral · porta ÚNICA abrindo para a área gourmet</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
-          <t>suíte, banheiro do quarto e banheiro do térreo (agora no fundo da cozinha, faixa SO)</t>
+          <t>suíte, banheiro do quarto e banheiro do térreo (canto SO/SE, porta p/ a área gourmet)</t>
         </is>
       </c>
     </row>
@@ -10050,179 +10050,6 @@
       <c r="M146" s="21" t="inlineStr">
         <is>
           <t>cotar empreiteiro/equipe separadamente do material · preencher o Fornecedor</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="16" t="inlineStr">
-        <is>
-          <t>IT144</t>
-        </is>
-      </c>
-      <c r="B147" s="17" t="inlineStr">
-        <is>
-          <t>Hidráulica</t>
-        </is>
-      </c>
-      <c r="C147" s="17" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="D147" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E147" s="16" t="inlineStr">
-        <is>
-          <t>Lavabo do térreo — vaso + cuba + torneira + sifão</t>
-        </is>
-      </c>
-      <c r="F147" s="16" t="inlineStr">
-        <is>
-          <t>lavabo 1,50 × 1,50 no canto SO/SE, porta p/ a varanda</t>
-        </is>
-      </c>
-      <c r="G147" s="16" t="inlineStr">
-        <is>
-          <t>cj</t>
-        </is>
-      </c>
-      <c r="H147" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I147" s="16">
-        <f>COUNTIFS(Cotações!$E$2:$E$2,$A147)</f>
-        <v/>
-      </c>
-      <c r="J147" s="32">
-        <f>IF(I147=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A147))</f>
-        <v/>
-      </c>
-      <c r="K147" s="17">
-        <f>IF(I147=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A147)*(Cotações!$J$2:$J$2=J147),0),0)),""))</f>
-        <v/>
-      </c>
-      <c r="L147" s="18">
-        <f>IF(I147=0,"—",IFERROR(J147*H147,""))</f>
-        <v/>
-      </c>
-      <c r="M147" s="16" t="inlineStr">
-        <is>
-          <t>ponto novo: ramal de esgoto e água aproveita a prumada do banheiro vizinho (paredes coladas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="21" t="inlineStr">
-        <is>
-          <t>IT145</t>
-        </is>
-      </c>
-      <c r="B148" s="22" t="inlineStr">
-        <is>
-          <t>Hidráulica</t>
-        </is>
-      </c>
-      <c r="C148" s="22" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="D148" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E148" s="21" t="inlineStr">
-        <is>
-          <t>Ramal hidráulico do lavabo (água fria + esgoto + ventilação)</t>
-        </is>
-      </c>
-      <c r="F148" s="21" t="inlineStr"/>
-      <c r="G148" s="21" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="H148" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I148" s="21">
-        <f>COUNTIFS(Cotações!$E$2:$E$2,$A148)</f>
-        <v/>
-      </c>
-      <c r="J148" s="30">
-        <f>IF(I148=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A148))</f>
-        <v/>
-      </c>
-      <c r="K148" s="22">
-        <f>IF(I148=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A148)*(Cotações!$J$2:$J$2=J148),0),0)),""))</f>
-        <v/>
-      </c>
-      <c r="L148" s="23">
-        <f>IF(I148=0,"—",IFERROR(J148*H148,""))</f>
-        <v/>
-      </c>
-      <c r="M148" s="21" t="inlineStr">
-        <is>
-          <t>economia: banheiro e lavabo compartilham a mesma parede hidráulica</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="16" t="inlineStr">
-        <is>
-          <t>IT146</t>
-        </is>
-      </c>
-      <c r="B149" s="17" t="inlineStr">
-        <is>
-          <t>Geral / Estrutura</t>
-        </is>
-      </c>
-      <c r="C149" s="17" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="D149" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E149" s="16" t="inlineStr">
-        <is>
-          <t>Acabamento do lavabo do térreo — microcimento + piso resinado</t>
-        </is>
-      </c>
-      <c r="F149" s="16" t="inlineStr">
-        <is>
-          <t>paredes + piso · sem carpete de pedra (lavabo seco)</t>
-        </is>
-      </c>
-      <c r="G149" s="16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="H149" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="I149" s="16">
-        <f>COUNTIFS(Cotações!$E$2:$E$2,$A149)</f>
-        <v/>
-      </c>
-      <c r="J149" s="32">
-        <f>IF(I149=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A149))</f>
-        <v/>
-      </c>
-      <c r="K149" s="17">
-        <f>IF(I149=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A149)*(Cotações!$J$2:$J$2=J149),0),0)),""))</f>
-        <v/>
-      </c>
-      <c r="L149" s="18">
-        <f>IF(I149=0,"—",IFERROR(J149*H149,""))</f>
-        <v/>
-      </c>
-      <c r="M149" s="16" t="inlineStr">
-        <is>
-          <t>DIY viável — ambiente pequeno e sem área molhada</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11102,6 +10929,23 @@
       <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Faixa de luz 9,70 → 8,20 m · laje 68 → 70 m² · telha 98 → 100 m² · parede verde 14 → 12 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Banheiro e lavabo do térreo unificados em um só (1,50 × 2,50)</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Cozinha recupera ~1,9 m² · porta única p/ a área gourmet · −3 itens de lavabo</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 15:45 (BRT)</t>
+          <t>Gerada em 16/07/2026 15:52 (BRT)</t>
         </is>
       </c>
     </row>
@@ -854,19 +854,19 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Monolev ~340 m² líquidos — perímetro + térreo</t>
+          <t>Monolev ~320 m² líquidos — perímetro + estruturais do térreo (divisa da garagem, testada)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Divisórias do superior</t>
+          <t>Divisórias em Lightwall</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Lightwall 2P 90 mm ~80 m² (conceito mezanino: telhado apoia só no perímetro)</t>
+          <t>Lightwall 2P 90 mm ~100 m²: todo o pav. superior (conceito mezanino) + caixas do lavabo e do banheiro do térreo — nenhuma delas é estrutural</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Despensa (1,50 × 1,10) + bancada + banheiro completo único (1,50 × 2,50, sem box) no canto do fundo · janela p/ o acesso lateral · porta ÚNICA abrindo para a área gourmet</t>
+          <t>Lavabo 1,50 × 1,50 no canto da garagem c/ o corredor (janela p/ o corredor) · despensa (1,50 × 1,10) + bancada + banheiro completo (1,50 × 2,50, sem box) no fundo, porta ÚNICA p/ a área gourmet</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M146"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>Painéis EPS (Monolev) — parede líquida ESTRUTURAL (perímetro + térreo)</t>
+          <t>Painéis EPS (Monolev) — parede líquida ESTRUTURAL (perímetro + estruturais do térreo)</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr"/>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="H4" s="29" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="I4" s="21">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A4)</f>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t>divisórias do superior migradas p/ Lightwall (conceito mezanino)</t>
+          <t>divisórias não estruturais (lavabo e banheiro do térreo + todo o superior) migradas p/ Lightwall</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="H5" s="31" t="n">
-        <v>680</v>
+        <v>640</v>
       </c>
       <c r="I5" s="16">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A5)</f>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>2 faces × 340 m²</t>
+          <t>2 faces × 320 m²</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
-          <t>suíte, banheiro do quarto e banheiro do térreo (canto SO/SE, porta p/ a área gourmet)</t>
+          <t>suíte, banheiro do quarto e banheiro do térreo · o lavabo do térreo não leva ralo linear</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="E122" s="21" t="inlineStr">
         <is>
-          <t>Divisórias internas Lightwall 2P 90 mm — pavimento superior completo</t>
+          <t>Divisórias Lightwall 2P 90 mm — pav. superior completo + lavabo e banheiro do térreo</t>
         </is>
       </c>
       <c r="F122" s="21" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="H122" s="29" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I122" s="21">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A122)</f>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="M122" s="21" t="inlineStr">
         <is>
-          <t>todas as internas do superior (mezanino, lavabo, banheiros, quarto, copa, corredor, closet, transversal da suíte) · hidráulica pesada em shaft (cava ≤ 50%) · juntas dissimilares Monolev↔Lightwall c/ tela 10 cm cada lado · içamento: painéis içados pelo vazio antes do fechamento</t>
+          <t>superior: todas as internas · térreo: caixa do lavabo (canto garagem/corredor) e do banheiro do fundo · hidráulica pesada em shaft ou no radier (cava ≤ 50% = 45 mm: NÃO passa esgoto de 100 mm) · juntas dissimilares Monolev↔Lightwall c/ tela 10 cm cada lado</t>
         </is>
       </c>
     </row>
@@ -10050,6 +10050,179 @@
       <c r="M146" s="21" t="inlineStr">
         <is>
           <t>cotar empreiteiro/equipe separadamente do material · preencher o Fornecedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>IT144</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>Lavabo do térreo — vaso + cuba + torneira + sifão</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr">
+        <is>
+          <t>lavabo 1,50 × 1,50 no canto da garagem c/ o corredor lateral · janela p/ o corredor</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>cj</t>
+        </is>
+      </c>
+      <c r="H147" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A147)</f>
+        <v/>
+      </c>
+      <c r="J147" s="32">
+        <f>IF(I147=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A147))</f>
+        <v/>
+      </c>
+      <c r="K147" s="17">
+        <f>IF(I147=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A147)*(Cotações!$J$2:$J$2=J147),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L147" s="18">
+        <f>IF(I147=0,"—",IFERROR(J147*H147,""))</f>
+        <v/>
+      </c>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>CRÍTICO: esgoto de 100 mm do vaso NÃO cabe em painel Lightwall de 90 mm — sai pelo RADIER, posição congelada antes da concretagem (etapa 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="21" t="inlineStr">
+        <is>
+          <t>IT145</t>
+        </is>
+      </c>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C148" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" s="21" t="inlineStr">
+        <is>
+          <t>Ramal hidráulico do lavabo do térreo (água fria + esgoto + ventilação)</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="inlineStr"/>
+      <c r="G148" s="21" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H148" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A148)</f>
+        <v/>
+      </c>
+      <c r="J148" s="30">
+        <f>IF(I148=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A148))</f>
+        <v/>
+      </c>
+      <c r="K148" s="22">
+        <f>IF(I148=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A148)*(Cotações!$J$2:$J$2=J148),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L148" s="23">
+        <f>IF(I148=0,"—",IFERROR(J148*H148,""))</f>
+        <v/>
+      </c>
+      <c r="M148" s="21" t="inlineStr">
+        <is>
+          <t>ramal embutido no radier · prumada de ventilação pela parede Monolev do corredor</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>IT146</t>
+        </is>
+      </c>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>Acabamento do lavabo do térreo — microcimento + piso resinado</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr">
+        <is>
+          <t>paredes + piso · lavabo seco, sem carpete de pedra</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H149" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="I149" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A149)</f>
+        <v/>
+      </c>
+      <c r="J149" s="32">
+        <f>IF(I149=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A149))</f>
+        <v/>
+      </c>
+      <c r="K149" s="17">
+        <f>IF(I149=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A149)*(Cotações!$J$2:$J$2=J149),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L149" s="18">
+        <f>IF(I149=0,"—",IFERROR(J149*H149,""))</f>
+        <v/>
+      </c>
+      <c r="M149" s="16" t="inlineStr">
+        <is>
+          <t>base cimentícia do Lightwall recebe microcimento direto · DIY viável</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10945,7 +11118,41 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Cozinha recupera ~1,9 m² · porta única p/ a área gourmet · −3 itens de lavabo</t>
+          <t>Cozinha recupera ~1,9 m² · porta única p/ a área gourmet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Lavabo 1,50 × 1,50 no canto da garagem c/ o corredor (janela p/ o corredor)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Térreo volta a ter banheiro acessível por dentro</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Divisórias do térreo (lavabo e banheiro) em Lightwall, não Monolev</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Monolev 340 → 320 m² · Lightwall 80 → 100 m² · esgoto de 100 mm obrigatoriamente pelo radier</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 15:52 (BRT)</t>
+          <t>Gerada em 16/07/2026 21:09 (BRT)</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11153,6 +11153,23 @@
       <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Monolev 340 → 320 m² · Lightwall 80 → 100 m² · esgoto de 100 mm obrigatoriamente pelo radier</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Superior: copa desce 1 m; corredor avança 1 m na suíte; porta da suíte na lateral (closet recuado)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Quarto 3,70 → 4,70 m (10 → 11,8 m²) · suíte 4,50 → 3,50 m · closet passante 1,20 × 2,50 · suíte sem janela na viela (luz pelo vidro da extensão)</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 16/07/2026 21:09 (BRT)</t>
+          <t>Gerada em 18/07/2026 15:08 (BRT)</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10225,6 +10225,120 @@
           <t>base cimentícia do Lightwall recebe microcimento direto · DIY viável</t>
         </is>
       </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="21" t="inlineStr">
+        <is>
+          <t>IT147</t>
+        </is>
+      </c>
+      <c r="B150" s="22" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E150" s="21" t="inlineStr">
+        <is>
+          <t>Cobogó — parede flutuante em frente ao janelão (fachada NO)</t>
+        </is>
+      </c>
+      <c r="F150" s="21" t="inlineStr">
+        <is>
+          <t>h=3,50 m · afastada 1,00 m do janelão · do fim do vão da garagem até ~1 m além da janela · cerâmico ou concreto</t>
+        </is>
+      </c>
+      <c r="G150" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H150" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="I150" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A150)</f>
+        <v/>
+      </c>
+      <c r="J150" s="30">
+        <f>IF(I150=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A150))</f>
+        <v/>
+      </c>
+      <c r="K150" s="22">
+        <f>IF(I150=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A150)*(Cotações!$J$2:$J$2=J150),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L150" s="23">
+        <f>IF(I150=0,"—",IFERROR(J150*H150,""))</f>
+        <v/>
+      </c>
+      <c r="M150" s="21" t="inlineStr">
+        <is>
+          <t>sapata corrida própria + pilaretes a cada 2,5-3 m + cinta de coroamento no topo (resiste a vento, não é só empilhado) · cria câmara de ar ventilada contra o janelão (efeito chaminé) em vez de metal colado no vidro</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>IT148</t>
+        </is>
+      </c>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>Mão de obra</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>mão de obra</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>Mão de obra — fundação e elevação do cobogó (parede flutuante)</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>sapata + pilaretes + assentamento do cobogó + cinta de coroamento</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H151" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A151)</f>
+        <v/>
+      </c>
+      <c r="J151" s="32">
+        <f>IF(I151=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A151))</f>
+        <v/>
+      </c>
+      <c r="K151" s="17">
+        <f>IF(I151=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A151)*(Cotações!$J$2:$J$2=J151),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L151" s="18">
+        <f>IF(I151=0,"—",IFERROR(J151*H151,""))</f>
+        <v/>
+      </c>
+      <c r="M151" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10801,7 +10915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11170,6 +11284,40 @@
       <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Quarto 3,70 → 4,70 m (10 → 11,8 m²) · suíte 4,50 → 3,50 m · closet passante 1,20 × 2,50 · suíte sem janela na viela (luz pelo vidro da extensão)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Corredor reto, porta da suíte de frente no fim do corredor (desfeita a porta lateral); parede do closet removida (ficava dupla c/ a do corredor)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Closet passa de 1,20 → 1,60 m de largura; nicho natural atrás da parede do corredor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Cobogó em parede flutuante em frente ao janelão da fachada NO (h=3,50, afastado 1,00 m); porta de acesso à Luz 1 removida (a incluir depois); película espelhada restrita ao piso superior</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Câmara de ar ventilada evita transferência de calor para o vidro · térreo do janelão fica com vidro transparente</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 18/07/2026 15:08 (BRT)</t>
+          <t>Gerada em 18/07/2026 15:14 (BRT)</t>
         </is>
       </c>
     </row>
@@ -933,10 +933,22 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>Muro de divisa</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Pré-moldado (placa de concreto) 210 m² — 2 laterais (30,00 m cada, SO/viela + NE/vizinho) + fundo (10,00 m, SE) · h=3,00 m · frente (NO) sem muro (condomínio fechado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>Térreo — faixa SO</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Lavabo 1,50 × 1,50 no canto da garagem c/ o corredor (janela p/ o corredor) · despensa (1,50 × 1,10) + bancada + banheiro completo (1,50 × 2,50, sem box) no fundo, porta ÚNICA p/ a área gourmet</t>
         </is>
@@ -959,7 +971,8 @@
     <row r="31"/>
     <row r="32"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A30:D32"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
@@ -1140,14 +1153,14 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>Fundação — radier 103 m²</t>
+          <t>Fundação (radier 103 m²) + muro de divisa 210 m²</t>
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>19000</v>
+        <v>50500</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>26000</v>
+        <v>78500</v>
       </c>
       <c r="E4" s="24">
         <f>(C4+D4)/2</f>
@@ -1186,7 +1199,7 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>inclui eletroduto da ilha e hidráulica embutida</t>
+          <t>radier inclui eletroduto da ilha e hidráulica embutida · muro pré-moldado (placa) 210 m² (2×30,00 laterais + 10,00 fundo, h=3,00) — sistema mais econômico do mercado, ~30% mais barato que alvenaria convencional</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10339,6 +10352,124 @@
         <v/>
       </c>
       <c r="M151" s="16" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="21" t="inlineStr">
+        <is>
+          <t>IT149</t>
+        </is>
+      </c>
+      <c r="B152" s="22" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" s="21" t="inlineStr">
+        <is>
+          <t>Muro de divisa pré-moldado (placa de concreto) — 2 laterais + fundo</t>
+        </is>
+      </c>
+      <c r="F152" s="21" t="inlineStr">
+        <is>
+          <t>mourões "H" de concreto a cada 1,60-1,67 m + placas de concreto armado (3-3,5 cm) encaixadas, empilhadas até h=3,00 · pingadeira + chapéu de acabamento no topo</t>
+        </is>
+      </c>
+      <c r="G152" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="H152" s="29" t="n">
+        <v>210</v>
+      </c>
+      <c r="I152" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A152)</f>
+        <v/>
+      </c>
+      <c r="J152" s="30">
+        <f>IF(I152=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A152))</f>
+        <v/>
+      </c>
+      <c r="K152" s="22">
+        <f>IF(I152=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A152)*(Cotações!$J$2:$J$2=J152),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L152" s="23">
+        <f>IF(I152=0,"—",IFERROR(J152*H152,""))</f>
+        <v/>
+      </c>
+      <c r="M152" s="21" t="inlineStr">
+        <is>
+          <t>sistema MAIS ECONÔMICO do mercado (~30% mais barato que alvenaria+reboco+pintura) · 210 m² = 2×30,00 (viela SO + divisa NE) + 10,00 (fundo SE), h=3,00 · verificar carga de vento em muro isolado de 3,00 m (mourão/fundação dimensionados p/ altura, não é só empilhar) · trecho da divisa NE atrás do jardim de inverno recebe a parede verde como acabamento — não duplica estrutura</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>IT150</t>
+        </is>
+      </c>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>Mão de obra</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>mão de obra</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>Mão de obra — fundação + montagem do muro de divisa</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>fundação direta dos mourões + encaixe das placas + rejunte completo</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H153" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A153)</f>
+        <v/>
+      </c>
+      <c r="J153" s="32">
+        <f>IF(I153=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A153))</f>
+        <v/>
+      </c>
+      <c r="K153" s="17">
+        <f>IF(I153=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A153)*(Cotações!$J$2:$J$2=J153),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L153" s="18">
+        <f>IF(I153=0,"—",IFERROR(J153*H153,""))</f>
+        <v/>
+      </c>
+      <c r="M153" s="16" t="inlineStr">
+        <is>
+          <t>obra rápida por ser pré-moldado · recomendação: executar cedo (junto com o radier ou antes) para segurança do canteiro durante o restante da obra</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10550,7 +10681,7 @@
       </c>
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>Fundação — radier 103 m²</t>
+          <t>Fundação (radier 103 m²) + muro de divisa 210 m²</t>
         </is>
       </c>
       <c r="C4" s="23">
@@ -10915,7 +11046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11318,6 +11449,23 @@
       <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Câmara de ar ventilada evita transferência de calor para o vidro · térreo do janelão fica com vidro transparente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Muro de divisa pré-moldado nos 2 lados + fundo (210 m², h=3,00) — frente sem muro (condomínio fechado)</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Etapa 2 (fundação): R$ 45k → R$ 50,5-78,5k · total do projeto R$ 502-793k → R$ 533,5-845,5k</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 18/07/2026 15:14 (BRT)</t>
+          <t>Gerada em 18/07/2026 15:19 (BRT)</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="F150" s="21" t="inlineStr">
         <is>
-          <t>h=3,50 m · afastada 1,00 m do janelão · do fim do vão da garagem até ~1 m além da janela · cerâmico ou concreto</t>
+          <t>h=3,00 (mesma altura do muro de divisa) m · afastada 1,00 m do janelão · do fim do vão da garagem até ~1 m além da janela · cerâmico ou concreto</t>
         </is>
       </c>
       <c r="G150" s="21" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11466,6 +11466,23 @@
       <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Etapa 2 (fundação): R$ 45k → R$ 50,5-78,5k · total do projeto R$ 502-793k → R$ 533,5-845,5k</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Cobogó da fachada NO ajustado para h=3,00 (era 3,50) — mesma altura do muro de divisa</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Uniformiza a altura dos elementos verticais externos da casa</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 18/07/2026 15:19 (BRT)</t>
+          <t>Gerada em 18/07/2026 15:23 (BRT)</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="H150" s="29" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="I150" s="21">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A150)</f>
@@ -11046,7 +11046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11483,6 +11483,23 @@
       <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Uniformiza a altura dos elementos verticais externos da casa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Cobogó estendido até encostar no muro de divisa NE (antes parava ~0,80 m antes)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Vira estrutura contínua com o muro — 1 ponta apoiada no mourão do muro, só a ponta livre precisa de mourão próprio</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 18/07/2026 15:23 (BRT)</t>
+          <t>Gerada em 23/07/2026 20:18 (BRT)</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2100,10 +2100,14 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>Telas/acessórios de reforço (cantos, vãos)</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr"/>
+          <t>Telas de reforço e acessórios de canto — verba complementar</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>telas de vão (diagonais sobre cantos de janela/porta), reforços de ancoragem e arremates não cobertos pela cantoneira</t>
+        </is>
+      </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
           <t>vb</t>
@@ -2130,7 +2134,7 @@
       </c>
       <c r="M6" s="21" t="inlineStr">
         <is>
-          <t>verba — cotar no pacote do painel</t>
+          <t>cotar no pacote do painel · a cantoneira de canto está no item próprio (ver Cantoneira PVC c/ tela)</t>
         </is>
       </c>
     </row>
@@ -10468,6 +10472,65 @@
       <c r="M153" s="16" t="inlineStr">
         <is>
           <t>obra rápida por ser pré-moldado · recomendação: executar cedo (junto com o radier ou antes) para segurança do canteiro durante o restante da obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="21" t="inlineStr">
+        <is>
+          <t>IT151</t>
+        </is>
+      </c>
+      <c r="B154" s="22" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E154" s="21" t="inlineStr">
+        <is>
+          <t>Cantoneira de PVC com abas de tela — todos os cantos externos e vãos</t>
+        </is>
+      </c>
+      <c r="F154" s="21" t="inlineStr">
+        <is>
+          <t>perfil de PVC rígido c/ abas de fibra de vidro álcali-resistente, embutido no basecoat/argamassa projetada · aplicar em TODOS os cantos externos (vivos) e nas laterais e vergas de portas e janelas</t>
+        </is>
+      </c>
+      <c r="G154" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H154" s="29" t="n">
+        <v>321</v>
+      </c>
+      <c r="I154" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A154)</f>
+        <v/>
+      </c>
+      <c r="J154" s="30">
+        <f>IF(I154=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A154))</f>
+        <v/>
+      </c>
+      <c r="K154" s="22">
+        <f>IF(I154=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A154)*(Cotações!$J$2:$J$2=J154),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L154" s="23">
+        <f>IF(I154=0,"—",IFERROR(J154*H154,""))</f>
+        <v/>
+      </c>
+      <c r="M154" s="21" t="inlineStr">
+        <is>
+          <t>não corrói nem mancha (ao contrário de alumínio em massa cimentícia — meio alcalino ataca o Al) · integra-se ao revestimento, sem descolamento · 292 m medidos + 10% de recorte · térreo 168 m (inclui cantos de 6,00 m do vão duplo) · superior 115 m · externos 18 m · usar também na junta dissimilar Monolev↔Lightwall onde houver aresta</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11500,6 +11563,23 @@
       <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Vira estrutura contínua com o muro — 1 ponta apoiada no mourão do muro, só a ponta livre precisa de mourão próprio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Cantoneira de PVC c/ abas de tela especificada para TODOS os cantos externos e vãos (321 m)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Padroniza o arremate em Monolev e Lightwall · alumínio descartado em massa cimentícia (corrosão alcalina) · ~R$ 1,6-2,6 mil, dentro da etapa 4</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 23/07/2026 20:18 (BRT)</t>
+          <t>Gerada em 23/07/2026 23:41 (BRT)</t>
         </is>
       </c>
     </row>
@@ -3435,14 +3435,18 @@
           <t>Janelão vertical fachada noroeste (vidro laminado) + película espelhada</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr"/>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>parede da escada · 3,20 × 4,70 m · peitoril 1,00 · caixilho estruturado</t>
+        </is>
+      </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="H30" s="29" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="I30" s="21">
         <f>COUNTIFS(Cotações!$E$2:$E$2,$A30)</f>
@@ -3462,7 +3466,7 @@
       </c>
       <c r="M30" s="21" t="inlineStr">
         <is>
-          <t>parede da escada · ~2,2 × 4,70 m · peitoril 1,00 · caixilho estruturado</t>
+          <t>CORRIGIDO: largura alinhada à planta F-02 (era 2,2 m no catálogo e 2,4 m na elevação — a planta sempre mostrou 3,20 m, cobrindo todo o lance da escada) · película espelhada só no trecho do piso superior; térreo com vidro transparente</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11580,6 +11584,40 @@
       <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Padroniza o arremate em Monolev e Lightwall · alumínio descartado em massa cimentícia (corrosão alcalina) · ~R$ 1,6-2,6 mil, dentro da etapa 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Auditoria de orientação das folhas: planta e elevações conferidas e coerentes; marcadores NE/SO adicionados nas elevações</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>A elevação da rua é espelhada por convenção (NE à esquerda, SO à direita) — agora indicado na própria folha</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Janelão da escada corrigido para 3,20 x 4,70 m (havia 3 valores divergentes: 3,18 na planta, 2,40 na elevação, 2,20 no catálogo)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Vidro 10,5 -&gt; 15 m² · impacto na etapa 7 (esquadrias)</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 23/07/2026 23:41 (BRT)</t>
+          <t>Gerada em 27/07/2026 00:33 (BRT)</t>
         </is>
       </c>
     </row>
@@ -933,35 +933,40 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Muro de divisa</t>
+          <t>Exaustão da ilha</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Pré-moldado (placa de concreto) 210 m² — 2 laterais (30,00 m cada, SO/viela + NE/vizinho) + fundo (10,00 m, SE) · h=3,00 m · frente (NO) sem muro (condomínio fechado)</t>
+          <t>Plenum no forro c/ 2 frestas lineares de 30 mm + luz integrada · 1.100 m³/h · duto Ø250 · motor inline REMOTO na área técnica (32-38 dB(A) na cozinha) · liga sozinho pelo consumo do circuito do Invisacook</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Térreo — faixa SO</t>
+          <t>Área técnica</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Lavabo 1,50 × 1,50 no canto da garagem c/ o corredor (janela p/ o corredor) · despensa (1,50 × 1,10) + bancada + banheiro completo (1,50 × 2,50, sem box) no fundo, porta ÚNICA p/ a área gourmet</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+          <t>ABERTA (sem porta, só portão-gradil) — garante ar para a bomba de calor · acesso por escada marinheiro na parede da Luz 2 · equipamentos em IP65</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>COMO USAR</t>
         </is>
       </c>
-    </row>
-    <row r="30">
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Pré-moldado (placa de concreto) 210 m² — 2 laterais (30,00 m cada, SO/viela + NE/vizinho) + fundo (10,00 m, SE) · h=3,00 m · frente (NO) sem muro (condomínio fechado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Esta planilha é um EXPORT do painel de obra e é regerada a cada cotação lançada no site. Edições feitas aqui serão perdidas na próxima geração — lance tudo pelo site (pvizioli.github.io/projeto_casa_pedro) para que vire commit e volte para cá.</t>
@@ -971,7 +976,7 @@
     <row r="31"/>
     <row r="32"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="A30:D32"/>
     <mergeCell ref="B23:D23"/>
@@ -979,6 +984,8 @@
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
@@ -1870,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10535,6 +10542,415 @@
       <c r="M154" s="21" t="inlineStr">
         <is>
           <t>não corrói nem mancha (ao contrário de alumínio em massa cimentícia — meio alcalino ataca o Al) · integra-se ao revestimento, sem descolamento · 292 m medidos + 10% de recorte · térreo 168 m (inclui cantos de 6,00 m do vão duplo) · superior 115 m · externos 18 m · usar também na junta dissimilar Monolev↔Lightwall onde houver aresta</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>IT152</t>
+        </is>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>Climatização</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>Exaustão da ilha — plenum embutido no forro c/ 2 frestas lineares</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>plenum 1,40×0,90 no forro rebaixado sobre a ilha · 2 frestas de 30 mm × 2,60 m (uma de cada lado do painel de luz) · v=2,0 m/s · painel central removível p/ acesso aos filtros</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H155" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A155)</f>
+        <v/>
+      </c>
+      <c r="J155" s="32">
+        <f>IF(I155=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A155))</f>
+        <v/>
+      </c>
+      <c r="K155" s="17">
+        <f>IF(I155=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A155)*(Cotações!$J$2:$J$2=J155),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L155" s="18">
+        <f>IF(I155=0,"—",IFERROR(J155*H155,""))</f>
+        <v/>
+      </c>
+      <c r="M155" s="16" t="inlineStr">
+        <is>
+          <t>iluminação linear da ilha integrada entre as frestas — um só elemento faz luz e exaustão · desligada, lê-se como junta negativa no forro</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="21" t="inlineStr">
+        <is>
+          <t>IT153</t>
+        </is>
+      </c>
+      <c r="B156" s="22" t="inlineStr">
+        <is>
+          <t>Climatização</t>
+        </is>
+      </c>
+      <c r="C156" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E156" s="21" t="inlineStr">
+        <is>
+          <t>Motor inline remoto Ø250 + duto e filtros da exaustão</t>
+        </is>
+      </c>
+      <c r="F156" s="21" t="inlineStr">
+        <is>
+          <t>1.100 m³/h @ 200 Pa (~155 W de eixo) · duto liso Ø250 galv./inox ~10 m · 4 curvas · filtro de gordura metálico lavável · damper antirretorno · descarga em veneziana</t>
+        </is>
+      </c>
+      <c r="G156" s="21" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H156" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A156)</f>
+        <v/>
+      </c>
+      <c r="J156" s="30">
+        <f>IF(I156=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A156))</f>
+        <v/>
+      </c>
+      <c r="K156" s="22">
+        <f>IF(I156=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A156)*(Cotações!$J$2:$J$2=J156),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L156" s="23">
+        <f>IF(I156=0,"—",IFERROR(J156*H156,""))</f>
+        <v/>
+      </c>
+      <c r="M156" s="21" t="inlineStr">
+        <is>
+          <t>motor instalado na ÁREA TÉCNICA (~8 m da ilha, 2 lajes de permeio): 32-38 dB(A) na cozinha vs 55-65 de coifa convencional · v no duto 6,2 m/s (silencioso) · descarga afastada ≥3 m do vidro da suíte e da janela do quarto</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>IT154</t>
+        </is>
+      </c>
+      <c r="B157" s="17" t="inlineStr">
+        <is>
+          <t>Elétrica + Automação</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D157" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>Automação da exaustão — medidor no circuito do Invisacook + sensor de VOC/umidade</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr">
+        <is>
+          <t>medidor de energia c/ TC no circuito C13 (40 A) + sensor VOC/umidade no forro da cozinha + atuador de velocidade do inline · integração Home Assistant</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>cj</t>
+        </is>
+      </c>
+      <c r="H157" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A157)</f>
+        <v/>
+      </c>
+      <c r="J157" s="32">
+        <f>IF(I157=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A157))</f>
+        <v/>
+      </c>
+      <c r="K157" s="17">
+        <f>IF(I157=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A157)*(Cotações!$J$2:$J$2=J157),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L157" s="18">
+        <f>IF(I157=0,"—",IFERROR(J157*H157,""))</f>
+        <v/>
+      </c>
+      <c r="M157" s="16" t="inlineStr">
+        <is>
+          <t>o Invisacook não tem botão nem presença — ninguém lembra de ligar a coifa · lógica: potência&gt;200 W no C13 → exaustão em baixa; VOC/umidade escalona; desliga 10 min após o fim · &gt;50% abre a janela da Luz 2 (ar de reposição)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="21" t="inlineStr">
+        <is>
+          <t>IT155</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>Mão de obra</t>
+        </is>
+      </c>
+      <c r="C158" s="22" t="inlineStr">
+        <is>
+          <t>mão de obra</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E158" s="21" t="inlineStr">
+        <is>
+          <t>Mão de obra — exaustão da ilha (plenum, dutos, motor e comissionamento)</t>
+        </is>
+      </c>
+      <c r="F158" s="21" t="inlineStr">
+        <is>
+          <t>montagem do plenum no forro, dutos, motor inline, balanceamento e medição de vazão</t>
+        </is>
+      </c>
+      <c r="G158" s="21" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H158" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A158)</f>
+        <v/>
+      </c>
+      <c r="J158" s="30">
+        <f>IF(I158=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A158))</f>
+        <v/>
+      </c>
+      <c r="K158" s="22">
+        <f>IF(I158=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A158)*(Cotações!$J$2:$J$2=J158),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L158" s="23">
+        <f>IF(I158=0,"—",IFERROR(J158*H158,""))</f>
+        <v/>
+      </c>
+      <c r="M158" s="21" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>IT156</t>
+        </is>
+      </c>
+      <c r="B159" s="17" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>Portão-gradil da área técnica (sem porta — vão aberto p/ ventilação)</t>
+        </is>
+      </c>
+      <c r="F159" s="16" t="inlineStr">
+        <is>
+          <t>gradil metálico galvanizado c/ fechadura · vão ~1,20 × 2,00 · área técnica permanece ABERTA (sem folha cega)</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="H159" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A159)</f>
+        <v/>
+      </c>
+      <c r="J159" s="32">
+        <f>IF(I159=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A159))</f>
+        <v/>
+      </c>
+      <c r="K159" s="17">
+        <f>IF(I159=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A159)*(Cotações!$J$2:$J$2=J159),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L159" s="18">
+        <f>IF(I159=0,"—",IFERROR(J159*H159,""))</f>
+        <v/>
+      </c>
+      <c r="M159" s="16" t="inlineStr">
+        <is>
+          <t>CRÍTICO p/ a bomba de calor: BC AQS consome 250-400 m³/h e devolve o ar 4-6 °C mais frio · recinto de 11,5 m³ fechado faria o COP despencar (fabricantes exigem 15-20 m³ ou ventilação permanente) · aberta = ar infinito, COP nominal preservado · bônus: vazamento drena p/ fora, calor do rack dissipa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="21" t="inlineStr">
+        <is>
+          <t>IT157</t>
+        </is>
+      </c>
+      <c r="B160" s="22" t="inlineStr">
+        <is>
+          <t>Geral / Estrutura</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E160" s="21" t="inlineStr">
+        <is>
+          <t>Escada marinheiro de acesso à área técnica</t>
+        </is>
+      </c>
+      <c r="F160" s="21" t="inlineStr">
+        <is>
+          <t>metálica galvanizada · h=3,00 m · 10 degraus @0,30 · largura 0,40 · afastamento ≥0,15 da parede · prolongamento de 1,00 m acima do piso da técnica</t>
+        </is>
+      </c>
+      <c r="G160" s="21" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="H160" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A160)</f>
+        <v/>
+      </c>
+      <c r="J160" s="30">
+        <f>IF(I160=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A160))</f>
+        <v/>
+      </c>
+      <c r="K160" s="22">
+        <f>IF(I160=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A160)*(Cotações!$J$2:$J$2=J160),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L160" s="23">
+        <f>IF(I160=0,"—",IFERROR(J160*H160,""))</f>
+        <v/>
+      </c>
+      <c r="M160" s="21" t="inlineStr">
+        <is>
+          <t>fixada na parede da Luz 2 (varal) — acesso pelo pátio descoberto, sem entrar na casa · residencial não obriga gaiola (NR-35 é p/ ambiente de trabalho), mas o prolongamento + corrimão de apoio é o mínimo sensato</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="16" t="inlineStr">
+        <is>
+          <t>IT158</t>
+        </is>
+      </c>
+      <c r="B161" s="17" t="inlineStr">
+        <is>
+          <t>Elétrica + Automação</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D161" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>Proteção IP dos equipamentos da área técnica aberta</t>
+        </is>
+      </c>
+      <c r="F161" s="16" t="inlineStr">
+        <is>
+          <t>QDCA em quadro IP65 · rack de rede fechado c/ ventilação filtrada · tomadas IP54 · terminais protegidos</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H161" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A161)</f>
+        <v/>
+      </c>
+      <c r="J161" s="32">
+        <f>IF(I161=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A161))</f>
+        <v/>
+      </c>
+      <c r="K161" s="17">
+        <f>IF(I161=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A161)*(Cotações!$J$2:$J$2=J161),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L161" s="18">
+        <f>IF(I161=0,"—",IFERROR(J161*H161,""))</f>
+        <v/>
+      </c>
+      <c r="M161" s="16" t="inlineStr">
+        <is>
+          <t>consequência de manter a técnica aberta: chuva de vento e maresia urbana atingem os equipamentos · custo pequeno perto do ganho de COP da bomba de calor</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11618,6 +12034,40 @@
       <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Vidro 10,5 -&gt; 15 m² · impacto na etapa 7 (esquadrias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Exaustão da ilha: plenum embutido no forro c/ 2 frestas de 30 mm + luz linear integrada; motor inline remoto na área técnica; automação pelo consumo do circuito do Invisacook</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>1.100 m³/h @ 200 Pa · duto Ø250 (v=6,2 m/s) · 32-38 dB(A) na cozinha · NOVO PONTO SEM RETORNO: furo Ø250 na laje da técnica (etapa 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Área técnica passa a ser ABERTA (sem porta, portão-gradil) c/ escada marinheiro na parede da Luz 2</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Garante ar para a bomba de calor (11,5 m³ fechados seriam insuficientes; fabricantes exigem 15-20 m³ ou ventilação permanente) · exige equipamentos IP65</t>
         </is>
       </c>
     </row>

--- a/planilha-q22-l8.xlsx
+++ b/planilha-q22-l8.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gerada em 27/07/2026 00:33 (BRT)</t>
+          <t>Gerada em 27/07/2026 00:49 (BRT)</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Pré-moldado (placa de concreto) 210 m² — 2 laterais (30,00 m cada, SO/viela + NE/vizinho) + fundo (10,00 m, SE) · h=3,00 m · frente (NO) sem muro (condomínio fechado)</t>
+          <t>Calhas retangulares 150×100 nas 2 bordas longas (i=0,5% p/ o fundo) + 2 condutores Ø100 · I=172 mm/h · 108 m² de captação · rufos em chapa galv. #24</t>
         </is>
       </c>
     </row>
@@ -973,14 +973,29 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
+    <row r="31" ht="24" customHeight="1"/>
+    <row r="32" ht="24" customHeight="1"/>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Térreo — faixa SO</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Lavabo 1,50 × 1,50 no canto da garagem c/ o corredor (janela p/ o corredor) · despensa (1,50 × 1,10) + bancada + banheiro completo (1,50 × 2,50, sem box) no fundo, porta ÚNICA p/ a área gourmet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="A30:D32"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
@@ -1877,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2500,10 +2515,14 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>Rufos, calhas e arremates do lanternim</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr"/>
+          <t>Rufos e arremates — oitões, chaminé e lanternim</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>chapa galvanizada #24 (0,65 mm) ou alumínio · dobra ≥150 mm na parede e ≥200 mm sobre a telha, com pingadeira</t>
+        </is>
+      </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
           <t>vb</t>
@@ -2530,7 +2549,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>ponto crítico de estanqueidade</t>
+          <t>ponto crítico de estanqueidade · lanternim tem rufo de topo E de base (ver F-09) · calhas em item próprio</t>
         </is>
       </c>
     </row>
@@ -10951,6 +10970,360 @@
       <c r="M161" s="16" t="inlineStr">
         <is>
           <t>consequência de manter a técnica aberta: chuva de vento e maresia urbana atingem os equipamentos · custo pequeno perto do ganho de COP da bomba de calor</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="21" t="inlineStr">
+        <is>
+          <t>IT159</t>
+        </is>
+      </c>
+      <c r="B162" s="22" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E162" s="21" t="inlineStr">
+        <is>
+          <t>Calhas retangulares 150 × 100 mm — 2 bordas longas</t>
+        </is>
+      </c>
+      <c r="F162" s="21" t="inlineStr">
+        <is>
+          <t>chapa galvanizada #24 (0,65 mm) ou alumínio · declividade 0,5% para o fundo (SE) · suportes a cada 0,80 m · grelha folha-guarda</t>
+        </is>
+      </c>
+      <c r="G162" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H162" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="I162" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A162)</f>
+        <v/>
+      </c>
+      <c r="J162" s="30">
+        <f>IF(I162=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A162))</f>
+        <v/>
+      </c>
+      <c r="K162" s="22">
+        <f>IF(I162=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A162)*(Cotações!$J$2:$J$2=J162),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L162" s="23">
+        <f>IF(I162=0,"—",IFERROR(J162*H162,""))</f>
+        <v/>
+      </c>
+      <c r="M162" s="21" t="inlineStr">
+        <is>
+          <t>capacidade 443 L/min vs 169 L/min da calha mais carregada (folga 2,6×) · I=172 mm/h São Paulo T=5 anos · ver F-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>IT160</t>
+        </is>
+      </c>
+      <c r="B163" s="17" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C163" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D163" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>Condutores verticais Ø100 + coletor pluvial até a cisterna</t>
+        </is>
+      </c>
+      <c r="F163" s="16" t="inlineStr">
+        <is>
+          <t>2 descidas Ø100 (capacidade ~430 L/min cada) no fundo SE + coletor Ø100 i=1% ao longo da parede do fundo</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H163" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A163)</f>
+        <v/>
+      </c>
+      <c r="J163" s="32">
+        <f>IF(I163=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A163))</f>
+        <v/>
+      </c>
+      <c r="K163" s="17">
+        <f>IF(I163=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A163)*(Cotações!$J$2:$J$2=J163),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L163" s="18">
+        <f>IF(I163=0,"—",IFERROR(J163*H163,""))</f>
+        <v/>
+      </c>
+      <c r="M163" s="16" t="inlineStr">
+        <is>
+          <t>as duas calhas caem para o fundo → descidas chegam juntas na cisterna, sem coletor atravessando o quintal</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="21" t="inlineStr">
+        <is>
+          <t>IT161</t>
+        </is>
+      </c>
+      <c r="B164" s="22" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D164" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E164" s="21" t="inlineStr">
+        <is>
+          <t>Cisterna de água de chuva 5.000 L + filtro + descarte de primeira chuva</t>
+        </is>
+      </c>
+      <c r="F164" s="21" t="inlineStr">
+        <is>
+          <t>reservatório 5.000 L · filtro de malha 1 mm · dispositivo de first flush 216 L (2 mm × 108 m²) c/ dreno lento · extravasor com sifão e tela</t>
+        </is>
+      </c>
+      <c r="G164" s="21" t="inlineStr">
+        <is>
+          <t>cj</t>
+        </is>
+      </c>
+      <c r="H164" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A164)</f>
+        <v/>
+      </c>
+      <c r="J164" s="30">
+        <f>IF(I164=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A164))</f>
+        <v/>
+      </c>
+      <c r="K164" s="22">
+        <f>IF(I164=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A164)*(Cotações!$J$2:$J$2=J164),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L164" s="23">
+        <f>IF(I164=0,"—",IFERROR(J164*H164,""))</f>
+        <v/>
+      </c>
+      <c r="M164" s="21" t="inlineStr">
+        <is>
+          <t>NBR 15527 · potencial de captação 121 m³/ano (108 m² × 1.470 mm × 0,85 × 0,90) · autonomia 28 dias (irrigação+lavagem) ou 16 dias se alimentar vasos · POSIÇÃO A CONFIRMAR: parede do fundo SE, junto ao canto com o corredor SO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t>IT162</t>
+        </is>
+      </c>
+      <c r="B165" s="17" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D165" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t>Rede de água não potável + bomba da cisterna</t>
+        </is>
+      </c>
+      <c r="F165" s="16" t="inlineStr">
+        <is>
+          <t>bomba/pressurizador dedicado · tubulação em cor distinta (roxa) · placas "ÁGUA NÃO POTÁVEL" em todos os pontos de uso · pontos: parede verde, jardim frontal, quintal, torneiras de lavagem</t>
+        </is>
+      </c>
+      <c r="G165" s="16" t="inlineStr">
+        <is>
+          <t>vb</t>
+        </is>
+      </c>
+      <c r="H165" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A165)</f>
+        <v/>
+      </c>
+      <c r="J165" s="32">
+        <f>IF(I165=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A165))</f>
+        <v/>
+      </c>
+      <c r="K165" s="17">
+        <f>IF(I165=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A165)*(Cotações!$J$2:$J$2=J165),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L165" s="18">
+        <f>IF(I165=0,"—",IFERROR(J165*H165,""))</f>
+        <v/>
+      </c>
+      <c r="M165" s="16" t="inlineStr">
+        <is>
+          <t>SEPARAÇÃO ABSOLUTA da rede potável — sem interligação nem registro de emergência (NBR 15527) · mesma bomba alimenta a irrigação da parede verde, que já tinha ponto de água previsto</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="21" t="inlineStr">
+        <is>
+          <t>IT163</t>
+        </is>
+      </c>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D166" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E166" s="21" t="inlineStr">
+        <is>
+          <t>Caixa de gordura DUPLA (120 L, Ø600) + 3 caixas de inspeção 60×60</t>
+        </is>
+      </c>
+      <c r="F166" s="21" t="inlineStr">
+        <is>
+          <t>CG dupla recebendo cozinha + área gourmet · caixas de inspeção em mudanças de direção e a cada ≤25 m</t>
+        </is>
+      </c>
+      <c r="G166" s="21" t="inlineStr">
+        <is>
+          <t>cj</t>
+        </is>
+      </c>
+      <c r="H166" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="21">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A166)</f>
+        <v/>
+      </c>
+      <c r="J166" s="30">
+        <f>IF(I166=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A166))</f>
+        <v/>
+      </c>
+      <c r="K166" s="22">
+        <f>IF(I166=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A166)*(Cotações!$J$2:$J$2=J166),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L166" s="23">
+        <f>IF(I166=0,"—",IFERROR(J166*H166,""))</f>
+        <v/>
+      </c>
+      <c r="M166" s="21" t="inlineStr">
+        <is>
+          <t>a caixa simples (31 L) atende só 1 cozinha — a casa tem cozinha + pia do gourmet · CG recebe SÓ pias, nunca vaso · posicionar em local de acesso fácil (limpeza trimestral)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>IT164</t>
+        </is>
+      </c>
+      <c r="B167" s="17" t="inlineStr">
+        <is>
+          <t>Hidráulica</t>
+        </is>
+      </c>
+      <c r="C167" s="17" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D167" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>Reserva potável 3.000 L NO SOLO + pressurizador com inversor</t>
+        </is>
+      </c>
+      <c r="F167" s="16" t="inlineStr">
+        <is>
+          <t>reservatório 3.000 L no solo (enterrado ou aparente) · pressurizador com inversor (pressão constante) · alimenta manifolds da área técnica</t>
+        </is>
+      </c>
+      <c r="G167" s="16" t="inlineStr">
+        <is>
+          <t>cj</t>
+        </is>
+      </c>
+      <c r="H167" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="16">
+        <f>COUNTIFS(Cotações!$E$2:$E$2,$A167)</f>
+        <v/>
+      </c>
+      <c r="J167" s="32">
+        <f>IF(I167=0,"—",_xlfn.MINIFS(Cotações!$J$2:$J$2,Cotações!$E$2:$E$2,$A167))</f>
+        <v/>
+      </c>
+      <c r="K167" s="17">
+        <f>IF(I167=0,"—",IFERROR(INDEX(Cotações!$H$2:$H$2,MATCH(1,INDEX((Cotações!$E$2:$E$2=$A167)*(Cotações!$J$2:$J$2=J167),0),0)),""))</f>
+        <v/>
+      </c>
+      <c r="L167" s="18">
+        <f>IF(I167=0,"—",IFERROR(J167*H167,""))</f>
+        <v/>
+      </c>
+      <c r="M167" s="16" t="inlineStr">
+        <is>
+          <t>SUBSTITUI a caixa elevada: 1.000 L na laje da técnica = 1.630 kg em 4,8 m² = 340 kgf/m², contra 150 da NBR 6120 · no solo, a laje fica com 630 kg (131 kgf/m²) e a autonomia vai de 33 h para 100 h · contrapartida: sem energia não há água — avaliar caixa de 500 L de emergência (sobe p/ 235 kgf/m², exige reforço local) ou nobreak para o pressurizador</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12057,15 +12430,49 @@
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Hidrossanitário dimensionado e desenhado (F-11 água, F-12 esgoto, F-13 pluvial/cisterna)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Esgoto 50 UHC (Ø100 c/ folga de 4×) · caixa de gordura DUPLA · calhas 150×100 · cisterna 5.000 L · 3 folhas novas no caderno (13 no total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Reservação potável migra da laje da área técnica para o SOLO, com pressurizador</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>Caixa de 1.000 L na técnica = 340 kgf/m² (NBR 6120: 150) · no solo a laje fica em 131 kgf/m² e a autonomia sobe de 33 h para 100 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
           <t>24/07/2026</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>Área técnica passa a ser ABERTA (sem porta, portão-gradil) c/ escada marinheiro na parede da Luz 2</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Garante ar para a bomba de calor (11,5 m³ fechados seriam insuficientes; fabricantes exigem 15-20 m³ ou ventilação permanente) · exige equipamentos IP65</t>
         </is>
